--- a/Docs/KNOWLEDGE_BASE/REGISTRY/DOCUMENT_CONFLICT_REGISTER.xlsx
+++ b/Docs/KNOWLEDGE_BASE/REGISTRY/DOCUMENT_CONFLICT_REGISTER.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="Rf4c742bd49614e46"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="Rd1b5d765a4504da3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="1" r:id="R229b8c02fe864e4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="数据" sheetId="2" r:id="R81ccb73065e24a48"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -568,8 +568,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A5)</x:f>
-        <x:v>2</x:v>
+        <x:v>3</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -621,6 +620,23 @@
       </x:c>
       <x:c r="E5" t="str">
         <x:v>追加V72智能决策、Arena、模型和后续缺口记录；既有行保持不变。</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6">
+      <x:c r="A6" t="str">
+        <x:v>DOCUMENT_CONFLICT_REGISTER.xlsx</x:v>
+      </x:c>
+      <x:c r="B6" t="str">
+        <x:v>LUOYANG-184-T4-LIVING-WORLD-COMPLETION-MASTER-V1</x:v>
+      </x:c>
+      <x:c r="C6" t="n">
+        <x:v>29</x:v>
+      </x:c>
+      <x:c r="D6" t="n">
+        <x:v>1</x:v>
+      </x:c>
+      <x:c r="E6" t="str">
+        <x:v>追加洛阳T4 Phase 0—19正式状态、完成证据与Deferred边界；既有行保持不变。</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -629,7 +645,7 @@
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rbc882184f95c4b94"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R52a33d2fde83404d"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -675,8 +691,7 @@
         <x:v>记录数</x:v>
       </x:c>
       <x:c r="B2" s="7" t="n">
-        <x:f>COUNTA(A4:A32)</x:f>
-        <x:v>29</x:v>
+        <x:v>30</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
@@ -1805,13 +1820,93 @@
         <x:v>不是第二套世界</x:v>
       </x:c>
     </x:row>
+    <x:row r="33">
+      <x:c r="A33" t="str">
+        <x:v>DOC-CONFLICT-LUOYANG-T4-001</x:v>
+      </x:c>
+      <x:c r="B33" t="str">
+        <x:v>LuoyangLivingWorld</x:v>
+      </x:c>
+      <x:c r="C33" t="str">
+        <x:v>Docs/TASK_LUOYANG_184_T4_LIVING_WORLD_COMPLETION_MASTER_V1.md</x:v>
+      </x:c>
+      <x:c r="D33" t="str">
+        <x:v>Existing frozen designs</x:v>
+      </x:c>
+      <x:c r="E33" t="str">
+        <x:v>本任务未发现新的Frozen Design实质冲突</x:v>
+      </x:c>
+      <x:c r="F33" t="str">
+        <x:v>AGENTS、M12、统一Cell世界及资源守恒规则保持优先</x:v>
+      </x:c>
+      <x:c r="G33" t="str">
+        <x:v>用户总任务与仓库规则一致</x:v>
+      </x:c>
+      <x:c r="H33" t="str">
+        <x:v>RESOLVED_NO_CONFLICT</x:v>
+      </x:c>
+      <x:c r="I33" t="str">
+        <x:v>保留Deferred清单并按总纲路由后续工作</x:v>
+      </x:c>
+      <x:c r="J33" t="str">
+        <x:v>静默扩大范围或制造第二套世界</x:v>
+      </x:c>
+      <x:c r="K33"/>
+      <x:c r="L33" t="str">
+        <x:v>No conflict found</x:v>
+      </x:c>
+      <x:c r="M33" t="str">
+        <x:v>RESOLVED</x:v>
+      </x:c>
+      <x:c r="N33" t="str">
+        <x:v>T4 completion audit</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34">
+      <x:c r="A34" t="str">
+        <x:v>conflict.map-presentation.second-world.v1</x:v>
+      </x:c>
+      <x:c r="B34" t="str">
+        <x:v>MapPresentation</x:v>
+      </x:c>
+      <x:c r="C34" t="str">
+        <x:v>Docs/TASK_LUOYANG_PLAYABLE_VERTICAL_SLICE_MAP_PRESENTATION_AND_CONSTRUCTION_ASSET_LIBRARY_V1.md</x:v>
+      </x:c>
+      <x:c r="D34" t="str">
+        <x:v>Legacy debug scenes</x:v>
+      </x:c>
+      <x:c r="E34" t="str">
+        <x:v>Scene props or background art could be mistaken for authoritative city facts.</x:v>
+      </x:c>
+      <x:c r="F34" t="str">
+        <x:v>Runtime Cell/Facility/Person/Shipment facts always win; visual anchors are projections.</x:v>
+      </x:c>
+      <x:c r="G34" t="str">
+        <x:v>AGENTS and task constitution</x:v>
+      </x:c>
+      <x:c r="H34" t="str">
+        <x:v>RESOLVED_BY_VISUAL_PROJECTION_CONTRACT</x:v>
+      </x:c>
+      <x:c r="I34" t="str">
+        <x:v>Retain binding tests</x:v>
+      </x:c>
+      <x:c r="J34" t="str">
+        <x:v>Duplicate world truth</x:v>
+      </x:c>
+      <x:c r="K34" t="str"/>
+      <x:c r="L34" t="str"/>
+      <x:c r="M34" t="str">
+        <x:v>MONITORED</x:v>
+      </x:c>
+      <x:c r="N34" t="str"/>
+    </x:row>
   </x:sheetData>
   <x:mergeCells>
     <x:mergeCell ref="A1:L1"/>
   </x:mergeCells>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R32f6a08cdd964cb9"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd7685acff4084df2"/>
   </x:tableParts>
 </x:worksheet>
 </file>